--- a/TESTS/zlit_6_vern.xlsx
+++ b/TESTS/zlit_6_vern.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Жуль Верн — французький письменник-фантаст батько пригодницького та наукового роману</t>
+          <t>Жуль Верн</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Франція — Верн народився в Нанті і є одним із засновників жанру науково-фантастичного роману</t>
+          <t>Франція</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Поєднання захоплюючих пригод з науковими знаннями — його романи навчали і захоплювали одночасно</t>
+          <t>Поєднання захоплюючих пригод з науковими знаннями</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Дік Сенд — п'ятнадцятирічний юнга що змушений стати капітаном після загибелі екіпажу</t>
+          <t>Дік Сенд</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Досвідчений капітан і майже весь екіпаж загинули під час полювання на кита — хлопець залишився єдиним здатним управляти судном</t>
+          <t>Досвідчений капітан і майже весь екіпаж загинули під час полювання на кита</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -813,6 +843,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Підклав залізний предмет поруч з компасом — компас показував неправильний напрямок і ніхто цього не знав</t>
+          <t>Підклав залізний предмет поруч з компасом</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>В Африці де на них чекає рабство і полон — Негоро продає їх работорговцям</t>
+          <t>В Африці де на них чекає рабство і полон</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чим займався корабель «Пілігрим» перед тим, як втратив капітана і екіпаж?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Перевозив пасажирів</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Полював на китів у південних морях</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Возив пошту</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Досліджував Арктику</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що сталося з капітаном Гулем і більшістю матросів під час полювання на кита?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони втекли</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шлюпку з ними розбив підбитий кит, і вони всі загинули</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони здалися в полон</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони захворіли</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Хто залишився на борту «Пілігрима» після цієї трагедії, крім Діка Сенда?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише Дік Сенд один</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пасажири (місіс Уелдон з сином), кок Негоро, кілька матросів-новачків і силач Геркулес</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нікого, корабель був порожній</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише капітан Гуль вижив</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Хто така місіс Уелдон у романі?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Капітанка корабля</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пасажирка — дружина власника корабля, яка повертається додому з маленьким сином</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Куховарка</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Работорговиця</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Скільки років малому Джеку, сину місіс Уелдон?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Шістнадцять</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>П'ять років, він ще зовсім дитина</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Десять</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дорослий</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як присутність місіс Уелдон і маленького Джека впливала на відповідальність Діка Сенда?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не впливала</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дік відчував особливу відповідальність за їхню безпеку, окрім обов'язків капітана</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона їх ненавиділа</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дік їх уникав</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Як Дік Сенд намагався визначати курс корабля, не маючи досвіду штурмана?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він здався і не намагався</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Старанно вів розрахунки за компасом, лотом і досвідом, отриманим від капітана Гуля</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він плив навмання</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він довірив усе Негоро</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як команда (матроси-новачки) ставилась до того, що капітаном став підліток Дік Сенд?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зневажали і не слухали</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З довірою і повагою, бо бачили його старанність і відповідальність</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Підняли бунт</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Втекли з корабля</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>На кого з команди Дік Сенд міг покластися найбільше у фізично важкій роботі?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На Негоро</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На Геркулеса — силача, відданого і чесного матроса</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На місіс Уелдон</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На Джека</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що Дік Сенд зрозумів, коли побачили землю, яку вважали Південною Америкою?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Все було як і планувалось</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Місцевість і рослинність зовсім не схожі на Південну Америку — щось пішло не так із курсом</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Земля виявилась островом</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони повернулись додому</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чому компас показував неправильний курс протягом усієї подорожі?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Компас зламався випадково</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Негоро таємно підклав металевий предмет (магніт) біля компаса, щоб збити корабель з курсу</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Буря зіпсувала компас</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дік Сенд переплутав напрямки</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Куди насправді прибув корабель «Пілігрим» замість Америки?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>До Австралії</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До берегів Анголи в Африці — небезпечного для них регіону работоргівлі</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>До Індії</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Назад до Нової Зеландії</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Кого подорожні зустріли на африканському березі, і ким він представився?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Місцевого вождя</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Американця Гарріса, який запропонував провести їх до «найближчої американської ферми»</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Французького дослідника</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Работорговця відкрито</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Чим Гарріс насправді займався, попри привітну поведінку?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він був чесним фермером</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він був пов'язаний з работорговцями і навмисно вів подорожніх у пастку</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був заблукалим моряком</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він шукав золото</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що допомогло викрити справжню природу Гарріса?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він сам зізнався</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пес Дінго люто загарчав на Гарріса, як і на Негоро — пес упізнав у них спільників-работорговців</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Місіс Уелдон побачила документи</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гарріс заблукав</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Яке минуле мав Негоро до того, як став коком на «Пілігримі»?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він був чесним моряком завжди</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він був пов'язаний з работорговцями і мав особисті рахунки з капітаном Гулем</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був лікарем</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він був багатим купцем</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому Негоро навмисно скерував корабель до Африки, а не до Америки?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він заблукав сам</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Африканське побережжя, куди вони потрапили, контролювали работорговці, з якими Негоро був пов'язаний</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він хотів побачити рідне місто</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Випадковість</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як Негоро ставився до місіс Уелдон, Джека та інших протягом подорожі?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Допомагав їм щиро</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Приховано діяв проти них, маючи власні корисливі плани</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Захищав їх від усіх небезпек</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Був їм байдужий повністю</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що зрештою сталося з полоненими (місіс Уелдон, Джеком та іншими) в Африці?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони одразу втекли самі</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дік Сенд, Геркулес та інші зрештою звільнили їх, і вони дісталися безпечного місця</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їх продали в рабство назавжди</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони здалися ворогам</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Якою стала роль Діка Сенда до кінця роману, порівняно з початком?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не змінилась</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З підлітка-учня він став справжнім, досвідченим і відповідальним капітаном</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він здався і втратив віру</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він покинув море назавжди</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яка доля спіткала Негоро наприкінці роману?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він став героєм</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його злочини були викриті, і він отримав справедливе покарання</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він зник безслідно</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому пробачили все</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яка характерна риса Жуля Верна як письменника?</t>
+          <t>Жуль Верн відомий тим, що поєднує захопливі пригоди з точними науковими і географічними знаннями.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яке значення має географічна точність у романах Верна?</t>
+          <t>Географічна точність у романах Верна не має значення — він описував вигадані, неіснуючі місця.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому романи Жуля Верна вважаються важливими для розвитку жанру?</t>
+          <t>Романи Жуля Верна вважаються важливими для розвитку науково-пригодницького роману як жанру.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яку соціальну тему порушує роман «П'ятнадцятирічний капітан»?</t>
+          <t>Роман «П'ятнадцятирічний капітан» порушує тему засудження работоргівлі в Африці XIX століття.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея роману?</t>
+          <t>Головна ідея роману — діти й підлітки не здатні нести жодної відповідальності в кризових ситуаціях.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що доводить Дік Сенд своїми діями протягом роману?</t>
+          <t>Своїми діями Дік Сенд доводить, що мужність, відповідальність і наполегливість дозволяють подолати найважчі випробування.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які труднощі долає Дік Сенд у романі?</t>
+          <t>Хто допомагав і хто шкодив подорожнім у романі?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Управління кораблем без досвіду</t>
+          <t>Геркулес допомагав</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Зрада Негоро і відхилення від курсу</t>
+          <t>Негоро шкодив</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Полон і загроза рабства</t>
+          <t>Гарріс допомагав чесно</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Повінь у відкритому морі</t>
+          <t>Пес Дінго допоміг викрити зрадників</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,Б,В</t>
+          <t>А,Б,Г</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Американський плантатор що проти рабства — представляє моральну позицію автора щодо цього злочину</t>
+          <t>Американський плантатор що проти рабства</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Зберігає мужність розум і не полишає надії на звільнення — справжній лідер незважаючи на вік</t>
+          <t>Зберігає мужність розум і не полишає надії на звільнення</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
